--- a/dataset/construct/dataset_splits/data_size/5_percent/merged/fold4.xlsx
+++ b/dataset/construct/dataset_splits/data_size/5_percent/merged/fold4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN9"/>
+  <dimension ref="A1:AK9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1094</v>
+        <v>1306</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,79 +625,79 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>74.44095254391971</v>
+        <v>86.2350005070094</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>21.6855368882395</v>
       </c>
       <c r="E2" t="n">
-        <v>25.3443526170798</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
+        <v>10.7</v>
       </c>
       <c r="I2" t="n">
-        <v>1550</v>
+        <v>136.9</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>420.7</v>
+        <v>220.2</v>
       </c>
       <c r="L2" t="n">
-        <v>199.2</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>296.8</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>916.7</v>
+        <v>13</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>32.5</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>32.5</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>35.2</v>
+        <v>20.85</v>
       </c>
       <c r="V2" t="n">
-        <v>35.2</v>
+        <v>0.23</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>20.912910618793</v>
       </c>
       <c r="X2" t="n">
-        <v>23.25</v>
+        <v>20.4698827870943</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.204633204633205</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>23.3002291825821</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>22.8943655965997</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>1</v>
@@ -727,36 +712,27 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -764,123 +740,114 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>85.2440515755317</v>
+        <v>74.7334821722818</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>30.1102788964582</v>
       </c>
       <c r="E3" t="n">
-        <v>21.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>575</v>
+      </c>
+      <c r="I3" t="n">
+        <v>273</v>
+      </c>
+      <c r="J3" t="n">
+        <v>224</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1072</v>
+      </c>
+      <c r="L3" t="n">
+        <v>16</v>
+      </c>
+      <c r="M3" t="n">
+        <v>60</v>
+      </c>
+      <c r="N3" t="n">
+        <v>29</v>
+      </c>
+      <c r="O3" t="n">
+        <v>105</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>18</v>
       </c>
-      <c r="I3" t="n">
-        <v>29100</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>166</v>
-      </c>
-      <c r="L3" t="n">
-        <v>24</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>18</v>
       </c>
-      <c r="N3" t="n">
-        <v>208</v>
-      </c>
-      <c r="O3" t="n">
-        <v>4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>8</v>
-      </c>
-      <c r="R3" t="n">
-        <v>17</v>
-      </c>
-      <c r="S3" t="n">
-        <v>17</v>
-      </c>
       <c r="T3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>24.35</v>
       </c>
       <c r="V3" t="n">
-        <v>24</v>
+        <v>0.16</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>24.1914947797301</v>
       </c>
       <c r="X3" t="n">
-        <v>20.3</v>
+        <v>23.7726133940886</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.234782608695652</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>20.3717850776674</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.1186577456453</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>138</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>53272626</v>
+        <v>53531320</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -888,75 +855,79 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>78.1683778234086</v>
+        <v>82.072553045859</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>23.4375</v>
       </c>
       <c r="E4" t="n">
-        <v>35.4308390022676</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>45</v>
+      </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>55</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>182</v>
+      </c>
+      <c r="I4" t="n">
+        <v>337</v>
+      </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="K4" t="n">
-        <v>513</v>
+        <v>663</v>
       </c>
       <c r="L4" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M4" t="n">
-        <v>173</v>
+        <v>276</v>
       </c>
       <c r="N4" t="n">
-        <v>863</v>
+        <v>93</v>
       </c>
       <c r="O4" t="n">
-        <v>376</v>
+        <v>544</v>
       </c>
       <c r="P4" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>718</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>196</v>
+        <v>24.8</v>
       </c>
       <c r="V4" t="n">
-        <v>196</v>
+        <v>0.22</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>25.91042473536056</v>
       </c>
       <c r="X4" t="n">
-        <v>27.2</v>
+        <v>24.89604407083738</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.23</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>86.5</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>558.7</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -974,33 +945,24 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>112</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>55543822</v>
+        <v>54054177</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1008,71 +970,77 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>80.6516084873374</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>87.0718685831622</v>
+      </c>
+      <c r="D5" t="n">
+        <v>20.829995193078</v>
+      </c>
       <c r="E5" t="n">
-        <v>28.0890109547143</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>59</v>
+      </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>55</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>242</v>
+      </c>
+      <c r="M5" t="n">
+        <v>246</v>
+      </c>
+      <c r="N5" t="n">
+        <v>250</v>
+      </c>
       <c r="O5" t="n">
-        <v>173.36021</v>
+        <v>738</v>
       </c>
       <c r="P5" t="n">
-        <v>282.02493</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>261.2987</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>716.68384</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>21.6</v>
       </c>
       <c r="V5" t="n">
-        <v>21</v>
+        <v>0.12</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>21.70873423773453</v>
       </c>
       <c r="X5" t="n">
-        <v>26.150581</v>
+        <v>21.33502137901016</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>86.43302</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>541.40906</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1093,24 +1061,15 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>51849085</v>
+        <v>54535871</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1118,85 +1077,83 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>75.65776865160851</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>75.41409993155369</v>
+      </c>
+      <c r="D6" t="n">
+        <v>32.8719723183391</v>
+      </c>
       <c r="E6" t="n">
-        <v>27.968016063681</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>53</v>
+      </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="n">
-        <v>60</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1275</v>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>709</v>
+        <v>234</v>
       </c>
       <c r="M6" t="n">
-        <v>611</v>
+        <v>131</v>
       </c>
       <c r="N6" t="n">
-        <v>2595</v>
+        <v>282</v>
       </c>
       <c r="O6" t="n">
-        <v>1211</v>
+        <v>647</v>
       </c>
       <c r="P6" t="n">
-        <v>668</v>
+        <v>16</v>
       </c>
       <c r="Q6" t="n">
-        <v>569</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2448</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>230</v>
+        <v>16</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>25.1</v>
       </c>
       <c r="V6" t="n">
-        <v>230</v>
+        <v>0.21</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>25.84676275812381</v>
       </c>
       <c r="X6" t="n">
-        <v>24.6</v>
+        <v>25.09216919422348</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>84.90000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>523.8</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1205,26 +1162,21 @@
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1</v>
+        <v>211</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
+        <v>178</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>54974064</v>
+        <v>54197905</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1232,68 +1184,74 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>76.6132785763176</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+        <v>89.9411362080767</v>
+      </c>
+      <c r="D7" t="n">
+        <v>25.6055363321799</v>
+      </c>
       <c r="E7" t="n">
-        <v>38.9415557470714</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>60</v>
+      </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="n">
-        <v>51</v>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>843</v>
+      </c>
+      <c r="M7" t="n">
+        <v>471</v>
+      </c>
+      <c r="N7" t="n">
+        <v>651</v>
+      </c>
       <c r="O7" t="n">
-        <v>953</v>
+        <v>1965</v>
       </c>
       <c r="P7" t="n">
-        <v>868</v>
+        <v>230</v>
       </c>
       <c r="Q7" t="n">
-        <v>675</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2497</v>
+        <v>136</v>
       </c>
       <c r="S7" t="n">
-        <v>418</v>
+        <v>366</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>189</v>
+        <v>24.1</v>
       </c>
       <c r="V7" t="n">
-        <v>606</v>
+        <v>0.21</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>24.41436827029674</v>
       </c>
       <c r="X7" t="n">
-        <v>26.6</v>
+        <v>23.89394508780932</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>93.5</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>622.9</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1302,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1311,30 +1269,17 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>184</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>52081005</v>
+        <v>54921492</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1342,86 +1287,80 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>93.3223819301848</v>
+        <v>74.8008213552361</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>30.5555555555556</v>
       </c>
       <c r="E8" t="n">
-        <v>25.9515570934256</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>35</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>451</v>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>473</v>
+        <v>415</v>
       </c>
       <c r="M8" t="n">
-        <v>114</v>
+        <v>713</v>
       </c>
       <c r="N8" t="n">
-        <v>1038</v>
+        <v>289</v>
       </c>
       <c r="O8" t="n">
-        <v>439</v>
+        <v>1417</v>
       </c>
       <c r="P8" t="n">
-        <v>363</v>
+        <v>12</v>
       </c>
       <c r="Q8" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>24.6</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>26.32422758739949</v>
       </c>
       <c r="X8" t="n">
-        <v>29.3</v>
+        <v>24.87045980339612</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>93.2</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>642.5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1439,20 +1378,15 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="AK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
+        <v>140</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>51799026</v>
+        <v>52259388</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1460,84 +1394,88 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>80.5119780971937</v>
+        <v>82.0999315537303</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>37.465564738292</v>
       </c>
       <c r="E9" t="n">
-        <v>25.7255174008556</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>437</v>
+      </c>
+      <c r="I9" t="n">
+        <v>667</v>
+      </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>556</v>
       </c>
       <c r="K9" t="n">
-        <v>1071</v>
+        <v>1660</v>
       </c>
       <c r="L9" t="n">
-        <v>497</v>
+        <v>437</v>
       </c>
       <c r="M9" t="n">
-        <v>734</v>
+        <v>667</v>
       </c>
       <c r="N9" t="n">
-        <v>2302</v>
+        <v>541</v>
       </c>
       <c r="O9" t="n">
-        <v>1071</v>
+        <v>1645</v>
       </c>
       <c r="P9" t="n">
-        <v>497</v>
+        <v>64</v>
       </c>
       <c r="Q9" t="n">
-        <v>727</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2295</v>
+        <v>457</v>
       </c>
       <c r="S9" t="n">
-        <v>35</v>
+        <v>521</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>28.4</v>
       </c>
       <c r="V9" t="n">
-        <v>35</v>
+        <v>0.18</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>29.06169260858009</v>
       </c>
       <c r="X9" t="n">
-        <v>31.9</v>
+        <v>28.68614156282325</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>789.5</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1555,16 +1493,11 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
+        <v>117</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
